--- a/linhas metropolitanas.xlsx
+++ b/linhas metropolitanas.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilherme.frade\Desktop\Backup Guilherme\BACKUP - Guilherme\BACKUP - Guilherme\Automacao_python\sistema_de_ouvidoria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA0D25AB-B692-483B-854D-3449BA630C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD48A878-7A6B-4940-AF8C-2713C36BE9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CE2D439F-D325-4880-B900-5A4B740D870D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CE2D439F-D325-4880-B900-5A4B740D870D}"/>
   </bookViews>
   <sheets>
     <sheet name="linhas metropolitanas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'linhas metropolitanas'!$A$5:$K$908</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6279,11 +6295,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -6624,13 +6640,15 @@
   <dimension ref="A1:K908"/>
   <sheetFormatPr defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="18" customWidth="1"/>
+    <col min="1" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="61" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" customWidth="1"/>
     <col min="8" max="8" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="12.75"/>
-    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="12.75"/>
-    <row r="3" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -6665,7 +6683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -6700,7 +6718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -6735,7 +6753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -6770,7 +6788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -6805,7 +6823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -6840,7 +6858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -6875,7 +6893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -6910,7 +6928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -6945,7 +6963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -6980,7 +6998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -7015,7 +7033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -7050,7 +7068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -7085,7 +7103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
@@ -7120,7 +7138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
@@ -7155,7 +7173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
@@ -7190,7 +7208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -7225,7 +7243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -7260,7 +7278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
@@ -7295,7 +7313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
@@ -7330,7 +7348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -7365,7 +7383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -7400,7 +7418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>11</v>
       </c>
@@ -7435,7 +7453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>11</v>
       </c>
@@ -7470,7 +7488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
@@ -7505,7 +7523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
@@ -7540,7 +7558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>11</v>
       </c>
@@ -7575,7 +7593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>11</v>
       </c>
@@ -7610,7 +7628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -7645,7 +7663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
@@ -7680,7 +7698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>11</v>
       </c>
@@ -7715,7 +7733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
@@ -7750,7 +7768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
@@ -7785,7 +7803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>11</v>
       </c>
@@ -7820,7 +7838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>11</v>
       </c>
@@ -7855,7 +7873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -7890,7 +7908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -7925,7 +7943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -7960,7 +7978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -7995,7 +8013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
@@ -8030,7 +8048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -8065,7 +8083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>11</v>
       </c>
@@ -8100,7 +8118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>11</v>
       </c>
@@ -8135,7 +8153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>11</v>
       </c>
@@ -8170,7 +8188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -8205,7 +8223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>11</v>
       </c>
@@ -8240,7 +8258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -8275,7 +8293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
@@ -8310,7 +8328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>11</v>
       </c>
@@ -8345,7 +8363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>11</v>
       </c>
@@ -8380,7 +8398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>11</v>
       </c>
@@ -8415,7 +8433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>11</v>
       </c>
@@ -8450,7 +8468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -8485,7 +8503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>11</v>
       </c>
@@ -8520,7 +8538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>11</v>
       </c>
@@ -8555,7 +8573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
@@ -8590,7 +8608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>11</v>
       </c>
@@ -8625,7 +8643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>11</v>
       </c>
@@ -8660,7 +8678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>11</v>
       </c>
@@ -8695,7 +8713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
@@ -8730,7 +8748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -8765,7 +8783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
@@ -8800,7 +8818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
@@ -8835,7 +8853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
@@ -8870,7 +8888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
@@ -8905,7 +8923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>11</v>
       </c>
@@ -8940,7 +8958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>11</v>
       </c>
@@ -8975,7 +8993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>11</v>
       </c>
@@ -9010,7 +9028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -9045,7 +9063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>11</v>
       </c>
@@ -9080,7 +9098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>11</v>
       </c>
@@ -9115,7 +9133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>11</v>
       </c>
@@ -9150,7 +9168,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>11</v>
       </c>
@@ -9185,7 +9203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>11</v>
       </c>
@@ -9220,7 +9238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>11</v>
       </c>
@@ -9255,7 +9273,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>11</v>
       </c>
@@ -9290,7 +9308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -9325,7 +9343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>11</v>
       </c>
@@ -9360,7 +9378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>11</v>
       </c>
@@ -9395,7 +9413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
@@ -9430,7 +9448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>11</v>
       </c>
@@ -9465,7 +9483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>11</v>
       </c>
@@ -9500,7 +9518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>11</v>
       </c>
@@ -9535,7 +9553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>11</v>
       </c>
@@ -9570,7 +9588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -9605,7 +9623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>11</v>
       </c>
@@ -9640,7 +9658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>11</v>
       </c>
@@ -9675,7 +9693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>11</v>
       </c>
@@ -9710,7 +9728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>11</v>
       </c>
@@ -9745,7 +9763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>11</v>
       </c>
@@ -9780,7 +9798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>11</v>
       </c>
@@ -9815,7 +9833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>11</v>
       </c>
@@ -9850,7 +9868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -9885,7 +9903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>11</v>
       </c>
@@ -9920,7 +9938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>11</v>
       </c>
@@ -9955,7 +9973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>11</v>
       </c>
@@ -9990,7 +10008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>11</v>
       </c>
@@ -10025,7 +10043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>11</v>
       </c>
@@ -10060,7 +10078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>11</v>
       </c>
@@ -10095,7 +10113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
@@ -10130,7 +10148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -10165,7 +10183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>11</v>
       </c>
@@ -10200,7 +10218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>11</v>
       </c>
@@ -10235,7 +10253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>11</v>
       </c>
@@ -10270,7 +10288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>11</v>
       </c>
@@ -10305,7 +10323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>11</v>
       </c>
@@ -10340,7 +10358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>11</v>
       </c>
@@ -10375,7 +10393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>11</v>
       </c>
@@ -10410,7 +10428,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -10445,7 +10463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>11</v>
       </c>
@@ -10480,7 +10498,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>11</v>
       </c>
@@ -10515,7 +10533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>11</v>
       </c>
@@ -10550,7 +10568,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>11</v>
       </c>
@@ -10585,7 +10603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>11</v>
       </c>
@@ -10620,7 +10638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>11</v>
       </c>
@@ -10655,7 +10673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>11</v>
       </c>
@@ -10690,7 +10708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -10725,7 +10743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>11</v>
       </c>
@@ -10760,7 +10778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>11</v>
       </c>
@@ -10795,7 +10813,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>11</v>
       </c>
@@ -10830,7 +10848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>11</v>
       </c>
@@ -10865,7 +10883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>11</v>
       </c>
@@ -10900,7 +10918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>11</v>
       </c>
@@ -10935,7 +10953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>11</v>
       </c>
@@ -10970,7 +10988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -11005,7 +11023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>11</v>
       </c>
@@ -11040,7 +11058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>11</v>
       </c>
@@ -11075,7 +11093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>11</v>
       </c>
@@ -11110,7 +11128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>11</v>
       </c>
@@ -11145,7 +11163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>11</v>
       </c>
@@ -11180,7 +11198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>11</v>
       </c>
@@ -11215,7 +11233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>11</v>
       </c>
@@ -11250,7 +11268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -11285,7 +11303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>11</v>
       </c>
@@ -11320,7 +11338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>11</v>
       </c>
@@ -11355,7 +11373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>11</v>
       </c>
@@ -11390,7 +11408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>11</v>
       </c>
@@ -11425,7 +11443,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>11</v>
       </c>
@@ -11460,7 +11478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>11</v>
       </c>
@@ -11495,7 +11513,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>11</v>
       </c>
@@ -11530,7 +11548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -11565,7 +11583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>11</v>
       </c>
@@ -11600,7 +11618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>11</v>
       </c>
@@ -11635,7 +11653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>11</v>
       </c>
@@ -11670,7 +11688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>11</v>
       </c>
@@ -11705,7 +11723,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>11</v>
       </c>
@@ -11740,7 +11758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>11</v>
       </c>
@@ -11775,7 +11793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>11</v>
       </c>
@@ -11810,7 +11828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -11845,7 +11863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>11</v>
       </c>
@@ -11880,7 +11898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>11</v>
       </c>
@@ -11915,7 +11933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
         <v>11</v>
       </c>
@@ -11950,7 +11968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>11</v>
       </c>
@@ -11985,7 +12003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
         <v>11</v>
       </c>
@@ -12020,7 +12038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>11</v>
       </c>
@@ -12055,7 +12073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>11</v>
       </c>
@@ -12090,7 +12108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -12125,7 +12143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>11</v>
       </c>
@@ -12160,7 +12178,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>11</v>
       </c>
@@ -12195,7 +12213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
         <v>11</v>
       </c>
@@ -12230,7 +12248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>11</v>
       </c>
@@ -12265,7 +12283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>11</v>
       </c>
@@ -12300,7 +12318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>11</v>
       </c>
@@ -12335,7 +12353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
         <v>11</v>
       </c>
@@ -12370,7 +12388,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>11</v>
       </c>
@@ -12405,7 +12423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
         <v>11</v>
       </c>
@@ -12440,7 +12458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>11</v>
       </c>
@@ -12475,7 +12493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
         <v>11</v>
       </c>
@@ -12510,7 +12528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>11</v>
       </c>
@@ -12545,7 +12563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
         <v>11</v>
       </c>
@@ -12580,7 +12598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>11</v>
       </c>
@@ -12615,7 +12633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>11</v>
       </c>
@@ -12650,7 +12668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>11</v>
       </c>
@@ -12685,7 +12703,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>11</v>
       </c>
@@ -12720,7 +12738,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>11</v>
       </c>
@@ -12755,7 +12773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
         <v>11</v>
       </c>
@@ -12790,7 +12808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>11</v>
       </c>
@@ -12825,7 +12843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
         <v>11</v>
       </c>
@@ -12860,7 +12878,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>11</v>
       </c>
@@ -12895,7 +12913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
         <v>11</v>
       </c>
@@ -12930,7 +12948,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>11</v>
       </c>
@@ -12965,7 +12983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
         <v>11</v>
       </c>
@@ -13000,7 +13018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>11</v>
       </c>
@@ -13035,7 +13053,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
         <v>11</v>
       </c>
@@ -13070,7 +13088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>11</v>
       </c>
@@ -13105,7 +13123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
         <v>11</v>
       </c>
@@ -13140,7 +13158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>11</v>
       </c>
@@ -13175,7 +13193,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
         <v>11</v>
       </c>
@@ -13210,7 +13228,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>11</v>
       </c>
@@ -13245,7 +13263,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
         <v>11</v>
       </c>
@@ -13280,7 +13298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>11</v>
       </c>
@@ -13315,7 +13333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
         <v>11</v>
       </c>
@@ -13350,7 +13368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>11</v>
       </c>
@@ -13385,7 +13403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
         <v>11</v>
       </c>
@@ -13420,7 +13438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>11</v>
       </c>
@@ -13455,7 +13473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
         <v>11</v>
       </c>
@@ -13490,7 +13508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>11</v>
       </c>
@@ -13525,7 +13543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>11</v>
       </c>
@@ -13560,7 +13578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>11</v>
       </c>
@@ -13595,7 +13613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
         <v>11</v>
       </c>
@@ -13630,7 +13648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>11</v>
       </c>
@@ -13665,7 +13683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
         <v>11</v>
       </c>
@@ -13700,7 +13718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>11</v>
       </c>
@@ -13735,7 +13753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
         <v>11</v>
       </c>
@@ -13770,7 +13788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>11</v>
       </c>
@@ -13805,7 +13823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
         <v>11</v>
       </c>
@@ -13840,7 +13858,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>11</v>
       </c>
@@ -13875,7 +13893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
         <v>11</v>
       </c>
@@ -13910,7 +13928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
         <v>11</v>
       </c>
@@ -13945,7 +13963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
         <v>11</v>
       </c>
@@ -13980,7 +13998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>11</v>
       </c>
@@ -14015,7 +14033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
         <v>11</v>
       </c>
@@ -14050,7 +14068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>11</v>
       </c>
@@ -14085,7 +14103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
         <v>11</v>
       </c>
@@ -14120,7 +14138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>11</v>
       </c>
@@ -14155,7 +14173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
         <v>11</v>
       </c>
@@ -14190,7 +14208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>11</v>
       </c>
@@ -14225,7 +14243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
         <v>11</v>
       </c>
@@ -14260,7 +14278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>11</v>
       </c>
@@ -14295,7 +14313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
         <v>11</v>
       </c>
@@ -14330,7 +14348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>11</v>
       </c>
@@ -14365,7 +14383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
         <v>11</v>
       </c>
@@ -14400,7 +14418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>11</v>
       </c>
@@ -14435,7 +14453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
         <v>11</v>
       </c>
@@ -14470,7 +14488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>11</v>
       </c>
@@ -14505,7 +14523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
         <v>11</v>
       </c>
@@ -14540,7 +14558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>11</v>
       </c>
@@ -14575,7 +14593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
         <v>11</v>
       </c>
@@ -14610,7 +14628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>11</v>
       </c>
@@ -14645,7 +14663,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
         <v>11</v>
       </c>
@@ -14680,7 +14698,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>11</v>
       </c>
@@ -14715,7 +14733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
         <v>11</v>
       </c>
@@ -14750,7 +14768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
         <v>11</v>
       </c>
@@ -14785,7 +14803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
         <v>11</v>
       </c>
@@ -14820,7 +14838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>11</v>
       </c>
@@ -14855,7 +14873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
         <v>11</v>
       </c>
@@ -14890,7 +14908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>11</v>
       </c>
@@ -14925,7 +14943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
         <v>11</v>
       </c>
@@ -14960,7 +14978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>11</v>
       </c>
@@ -14995,7 +15013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
         <v>11</v>
       </c>
@@ -15030,7 +15048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>11</v>
       </c>
@@ -15065,7 +15083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>11</v>
       </c>
@@ -15100,7 +15118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
         <v>11</v>
       </c>
@@ -15135,7 +15153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>11</v>
       </c>
@@ -15170,7 +15188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
         <v>11</v>
       </c>
@@ -15205,7 +15223,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
         <v>11</v>
       </c>
@@ -15240,7 +15258,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
         <v>11</v>
       </c>
@@ -15275,7 +15293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>11</v>
       </c>
@@ -15310,7 +15328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
         <v>11</v>
       </c>
@@ -15345,7 +15363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
         <v>11</v>
       </c>
@@ -15380,7 +15398,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
         <v>11</v>
       </c>
@@ -15415,7 +15433,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
         <v>11</v>
       </c>
@@ -15450,7 +15468,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>11</v>
       </c>
@@ -15485,7 +15503,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>11</v>
       </c>
@@ -15520,7 +15538,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
         <v>11</v>
       </c>
@@ -15555,7 +15573,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
         <v>11</v>
       </c>
@@ -15590,7 +15608,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
         <v>11</v>
       </c>
@@ -15625,7 +15643,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
         <v>11</v>
       </c>
@@ -15660,7 +15678,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
         <v>11</v>
       </c>
@@ -15695,7 +15713,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
         <v>11</v>
       </c>
@@ -15730,7 +15748,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
         <v>11</v>
       </c>
@@ -15765,7 +15783,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
         <v>11</v>
       </c>
@@ -15800,7 +15818,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>11</v>
       </c>
@@ -15835,7 +15853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>11</v>
       </c>
@@ -15870,7 +15888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>11</v>
       </c>
@@ -15905,7 +15923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>11</v>
       </c>
@@ -15940,7 +15958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>11</v>
       </c>
@@ -15975,7 +15993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
         <v>11</v>
       </c>
@@ -16010,7 +16028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>11</v>
       </c>
@@ -16045,7 +16063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
         <v>11</v>
       </c>
@@ -16080,7 +16098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
         <v>11</v>
       </c>
@@ -16115,7 +16133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
         <v>11</v>
       </c>
@@ -16150,7 +16168,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>11</v>
       </c>
@@ -16185,7 +16203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>11</v>
       </c>
@@ -16220,7 +16238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
         <v>11</v>
       </c>
@@ -16255,7 +16273,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
         <v>11</v>
       </c>
@@ -16290,7 +16308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
         <v>11</v>
       </c>
@@ -16325,7 +16343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
         <v>11</v>
       </c>
@@ -16360,7 +16378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
         <v>11</v>
       </c>
@@ -16395,7 +16413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
         <v>11</v>
       </c>
@@ -16430,7 +16448,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
         <v>11</v>
       </c>
@@ -16465,7 +16483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
         <v>11</v>
       </c>
@@ -16500,7 +16518,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
         <v>11</v>
       </c>
@@ -16535,7 +16553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>11</v>
       </c>
@@ -16570,7 +16588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
         <v>11</v>
       </c>
@@ -16605,7 +16623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
         <v>11</v>
       </c>
@@ -16640,7 +16658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
         <v>11</v>
       </c>
@@ -16675,7 +16693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
         <v>11</v>
       </c>
@@ -16710,7 +16728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
         <v>11</v>
       </c>
@@ -16745,7 +16763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
         <v>11</v>
       </c>
@@ -16780,7 +16798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
         <v>11</v>
       </c>
@@ -16815,7 +16833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
         <v>11</v>
       </c>
@@ -16850,7 +16868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
         <v>11</v>
       </c>
@@ -16885,7 +16903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
         <v>11</v>
       </c>
@@ -16920,7 +16938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
         <v>11</v>
       </c>
@@ -16955,7 +16973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
         <v>11</v>
       </c>
@@ -16990,7 +17008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
         <v>11</v>
       </c>
@@ -17025,7 +17043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
         <v>11</v>
       </c>
@@ -17060,7 +17078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
         <v>11</v>
       </c>
@@ -17095,7 +17113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
         <v>11</v>
       </c>
@@ -17130,7 +17148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
         <v>11</v>
       </c>
@@ -17165,7 +17183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
         <v>11</v>
       </c>
@@ -17200,7 +17218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
         <v>11</v>
       </c>
@@ -17235,7 +17253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
         <v>11</v>
       </c>
@@ -17270,7 +17288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
         <v>11</v>
       </c>
@@ -17305,7 +17323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
         <v>11</v>
       </c>
@@ -17340,7 +17358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
         <v>11</v>
       </c>
@@ -17375,7 +17393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
         <v>11</v>
       </c>
@@ -17410,7 +17428,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
         <v>11</v>
       </c>
@@ -17445,7 +17463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
         <v>11</v>
       </c>
@@ -17480,7 +17498,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
         <v>11</v>
       </c>
@@ -17515,7 +17533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="315" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
         <v>11</v>
       </c>
@@ -17550,7 +17568,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
         <v>11</v>
       </c>
@@ -17585,7 +17603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
         <v>11</v>
       </c>
@@ -17620,7 +17638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
         <v>11</v>
       </c>
@@ -17655,7 +17673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
         <v>11</v>
       </c>
@@ -17690,7 +17708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
         <v>11</v>
       </c>
@@ -17725,7 +17743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
         <v>11</v>
       </c>
@@ -17760,7 +17778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
         <v>11</v>
       </c>
@@ -17795,7 +17813,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
         <v>11</v>
       </c>
@@ -17830,7 +17848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
         <v>11</v>
       </c>
@@ -17865,7 +17883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
         <v>11</v>
       </c>
@@ -17900,7 +17918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
         <v>11</v>
       </c>
@@ -17935,7 +17953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
         <v>11</v>
       </c>
@@ -17970,7 +17988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
         <v>11</v>
       </c>
@@ -18005,7 +18023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
         <v>11</v>
       </c>
@@ -18040,7 +18058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
         <v>11</v>
       </c>
@@ -18075,7 +18093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
         <v>11</v>
       </c>
@@ -18110,7 +18128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
         <v>11</v>
       </c>
@@ -18145,7 +18163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
         <v>11</v>
       </c>
@@ -18180,7 +18198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
         <v>11</v>
       </c>
@@ -18215,7 +18233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
         <v>11</v>
       </c>
@@ -18250,7 +18268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
         <v>11</v>
       </c>
@@ -18285,7 +18303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
         <v>11</v>
       </c>
@@ -18320,7 +18338,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="338" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
         <v>11</v>
       </c>
@@ -18355,7 +18373,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="339" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
         <v>11</v>
       </c>
@@ -18390,7 +18408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="340" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
         <v>11</v>
       </c>
@@ -18425,7 +18443,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="341" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
         <v>11</v>
       </c>
@@ -18460,7 +18478,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="342" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
         <v>11</v>
       </c>
@@ -18495,7 +18513,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
         <v>11</v>
       </c>
@@ -18530,7 +18548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
         <v>11</v>
       </c>
@@ -18565,7 +18583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
         <v>11</v>
       </c>
@@ -18600,7 +18618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="346" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
         <v>11</v>
       </c>
@@ -18635,7 +18653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
         <v>11</v>
       </c>
@@ -18670,7 +18688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
         <v>11</v>
       </c>
@@ -18705,7 +18723,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
         <v>11</v>
       </c>
@@ -18740,7 +18758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
         <v>11</v>
       </c>
@@ -18775,7 +18793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
         <v>11</v>
       </c>
@@ -18810,7 +18828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="2" t="s">
         <v>11</v>
       </c>
@@ -18845,7 +18863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
         <v>11</v>
       </c>
@@ -18880,7 +18898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
         <v>11</v>
       </c>
@@ -18915,7 +18933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
         <v>11</v>
       </c>
@@ -18950,7 +18968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="2" t="s">
         <v>11</v>
       </c>
@@ -18985,7 +19003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="2" t="s">
         <v>11</v>
       </c>
@@ -19020,7 +19038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="2" t="s">
         <v>11</v>
       </c>
@@ -19055,7 +19073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
         <v>11</v>
       </c>
@@ -19090,7 +19108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="2" t="s">
         <v>11</v>
       </c>
@@ -19125,7 +19143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
         <v>11</v>
       </c>
@@ -19160,7 +19178,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
         <v>11</v>
       </c>
@@ -19195,7 +19213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
         <v>11</v>
       </c>
@@ -19230,7 +19248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="2" t="s">
         <v>11</v>
       </c>
@@ -19265,7 +19283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
         <v>11</v>
       </c>
@@ -19300,7 +19318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="2" t="s">
         <v>11</v>
       </c>
@@ -19335,7 +19353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
         <v>11</v>
       </c>
@@ -19370,7 +19388,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
         <v>11</v>
       </c>
@@ -19405,7 +19423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
         <v>11</v>
       </c>
@@ -19440,7 +19458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="370" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="2" t="s">
         <v>11</v>
       </c>
@@ -19475,7 +19493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="2" t="s">
         <v>11</v>
       </c>
@@ -19510,7 +19528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="2" t="s">
         <v>11</v>
       </c>
@@ -19545,7 +19563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
         <v>11</v>
       </c>
@@ -19580,7 +19598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="2" t="s">
         <v>11</v>
       </c>
@@ -19615,7 +19633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2" t="s">
         <v>11</v>
       </c>
@@ -19650,7 +19668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="376" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="2" t="s">
         <v>11</v>
       </c>
@@ -19685,7 +19703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2" t="s">
         <v>11</v>
       </c>
@@ -19720,7 +19738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="2" t="s">
         <v>11</v>
       </c>
@@ -19755,7 +19773,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="379" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="2" t="s">
         <v>11</v>
       </c>
@@ -19790,7 +19808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="2" t="s">
         <v>11</v>
       </c>
@@ -19825,7 +19843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2" t="s">
         <v>11</v>
       </c>
@@ -19860,7 +19878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="2" t="s">
         <v>11</v>
       </c>
@@ -19895,7 +19913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2" t="s">
         <v>11</v>
       </c>
@@ -19930,7 +19948,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="2" t="s">
         <v>11</v>
       </c>
@@ -19965,7 +19983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2" t="s">
         <v>11</v>
       </c>
@@ -20000,7 +20018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="2" t="s">
         <v>11</v>
       </c>
@@ -20035,7 +20053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="2" t="s">
         <v>11</v>
       </c>
@@ -20070,7 +20088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="2" t="s">
         <v>11</v>
       </c>
@@ -20105,7 +20123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="2" t="s">
         <v>11</v>
       </c>
@@ -20140,7 +20158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="2" t="s">
         <v>11</v>
       </c>
@@ -20175,7 +20193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="391" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="2" t="s">
         <v>11</v>
       </c>
@@ -20210,7 +20228,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="2" t="s">
         <v>11</v>
       </c>
@@ -20245,7 +20263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="2" t="s">
         <v>11</v>
       </c>
@@ -20280,7 +20298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="2" t="s">
         <v>11</v>
       </c>
@@ -20315,7 +20333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="2" t="s">
         <v>11</v>
       </c>
@@ -20350,7 +20368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="396" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="2" t="s">
         <v>11</v>
       </c>
@@ -20385,7 +20403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="2" t="s">
         <v>11</v>
       </c>
@@ -20420,7 +20438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="398" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="2" t="s">
         <v>11</v>
       </c>
@@ -20455,7 +20473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="2" t="s">
         <v>11</v>
       </c>
@@ -20490,7 +20508,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="400" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="2" t="s">
         <v>11</v>
       </c>
@@ -20525,7 +20543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
         <v>11</v>
       </c>
@@ -20560,7 +20578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="2" t="s">
         <v>11</v>
       </c>
@@ -20595,7 +20613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2" t="s">
         <v>11</v>
       </c>
@@ -20630,7 +20648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="2" t="s">
         <v>11</v>
       </c>
@@ -20665,7 +20683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="2" t="s">
         <v>11</v>
       </c>
@@ -20700,7 +20718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="2" t="s">
         <v>11</v>
       </c>
@@ -20735,7 +20753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="407" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="2" t="s">
         <v>11</v>
       </c>
@@ -20770,7 +20788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="2" t="s">
         <v>11</v>
       </c>
@@ -20805,7 +20823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="2" t="s">
         <v>11</v>
       </c>
@@ -20840,7 +20858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="2" t="s">
         <v>11</v>
       </c>
@@ -20875,7 +20893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="2" t="s">
         <v>11</v>
       </c>
@@ -20910,7 +20928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="2" t="s">
         <v>11</v>
       </c>
@@ -20945,7 +20963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="413" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="2" t="s">
         <v>11</v>
       </c>
@@ -20980,7 +20998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="2" t="s">
         <v>11</v>
       </c>
@@ -21015,7 +21033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
         <v>11</v>
       </c>
@@ -21050,7 +21068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="416" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="2" t="s">
         <v>11</v>
       </c>
@@ -21085,7 +21103,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="417" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="2" t="s">
         <v>11</v>
       </c>
@@ -21120,7 +21138,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="418" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="2" t="s">
         <v>11</v>
       </c>
@@ -21155,7 +21173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="2" t="s">
         <v>11</v>
       </c>
@@ -21190,7 +21208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="2" t="s">
         <v>11</v>
       </c>
@@ -21225,7 +21243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="421" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="2" t="s">
         <v>11</v>
       </c>
@@ -21260,7 +21278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="422" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="2" t="s">
         <v>11</v>
       </c>
@@ -21295,7 +21313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2" t="s">
         <v>11</v>
       </c>
@@ -21330,7 +21348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="424" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="2" t="s">
         <v>11</v>
       </c>
@@ -21365,7 +21383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="425" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2" t="s">
         <v>11</v>
       </c>
@@ -21400,7 +21418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="426" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="2" t="s">
         <v>11</v>
       </c>
@@ -21435,7 +21453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="427" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2" t="s">
         <v>11</v>
       </c>
@@ -21470,7 +21488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="428" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
         <v>11</v>
       </c>
@@ -21505,7 +21523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="2" t="s">
         <v>11</v>
       </c>
@@ -21540,7 +21558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="2" t="s">
         <v>11</v>
       </c>
@@ -21575,7 +21593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
         <v>11</v>
       </c>
@@ -21610,7 +21628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="432" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="2" t="s">
         <v>11</v>
       </c>
@@ -21645,7 +21663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2" t="s">
         <v>11</v>
       </c>
@@ -21680,7 +21698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="434" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="2" t="s">
         <v>11</v>
       </c>
@@ -21715,7 +21733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="2" t="s">
         <v>11</v>
       </c>
@@ -21750,7 +21768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="2" t="s">
         <v>11</v>
       </c>
@@ -21785,7 +21803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
         <v>11</v>
       </c>
@@ -21820,7 +21838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="438" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="2" t="s">
         <v>11</v>
       </c>
@@ -21855,7 +21873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
         <v>11</v>
       </c>
@@ -21890,7 +21908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="2" t="s">
         <v>11</v>
       </c>
@@ -21925,7 +21943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="2" t="s">
         <v>11</v>
       </c>
@@ -21960,7 +21978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="2" t="s">
         <v>11</v>
       </c>
@@ -21995,7 +22013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
         <v>11</v>
       </c>
@@ -22030,7 +22048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="444" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="2" t="s">
         <v>11</v>
       </c>
@@ -22065,7 +22083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22100,7 +22118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="446" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22135,7 +22153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="447" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22170,7 +22188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="448" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22205,7 +22223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22240,7 +22258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="450" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
         <v>11</v>
       </c>
@@ -22275,7 +22293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="451" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22310,7 +22328,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="452" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22345,7 +22363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="453" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22380,7 +22398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="454" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22415,7 +22433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22450,7 +22468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="456" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22485,7 +22503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="457" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22520,7 +22538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22555,7 +22573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
         <v>11</v>
       </c>
@@ -22590,7 +22608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="460" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="2" t="s">
         <v>11</v>
       </c>
@@ -22625,7 +22643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="461" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="2" t="s">
         <v>11</v>
       </c>
@@ -22660,7 +22678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="462" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="2" t="s">
         <v>11</v>
       </c>
@@ -22695,7 +22713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
         <v>11</v>
       </c>
@@ -22730,7 +22748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="464" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22765,7 +22783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="465" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22800,7 +22818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22835,7 +22853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22870,7 +22888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="468" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22905,7 +22923,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="469" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22940,7 +22958,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="470" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="2" t="s">
         <v>1011</v>
       </c>
@@ -22975,7 +22993,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="471" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23010,7 +23028,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="472" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23045,7 +23063,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="473" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23080,7 +23098,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="474" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23115,7 +23133,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="475" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
         <v>11</v>
       </c>
@@ -23150,7 +23168,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="476" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23185,7 +23203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="477" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23220,7 +23238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="478" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23255,7 +23273,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="479" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23290,7 +23308,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="480" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23325,7 +23343,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="481" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23360,7 +23378,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="482" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23395,7 +23413,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="483" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23430,7 +23448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="2" t="s">
         <v>11</v>
       </c>
@@ -23465,7 +23483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="485" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="2" t="s">
         <v>11</v>
       </c>
@@ -23500,7 +23518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="486" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
         <v>11</v>
       </c>
@@ -23535,7 +23553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="487" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
         <v>11</v>
       </c>
@@ -23570,7 +23588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="488" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
         <v>11</v>
       </c>
@@ -23605,7 +23623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="489" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="2" t="s">
         <v>11</v>
       </c>
@@ -23640,7 +23658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="2" t="s">
         <v>11</v>
       </c>
@@ -23675,7 +23693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="491" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23710,7 +23728,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="492" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23745,7 +23763,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="493" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23780,7 +23798,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="494" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23815,7 +23833,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="495" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23850,7 +23868,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="496" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23885,7 +23903,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="497" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23920,7 +23938,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="498" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23955,7 +23973,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="499" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="2" t="s">
         <v>1011</v>
       </c>
@@ -23990,7 +24008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="500" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24025,7 +24043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="501" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="2" t="s">
         <v>11</v>
       </c>
@@ -24060,7 +24078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="502" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24095,7 +24113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="503" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24130,7 +24148,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="504" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24165,7 +24183,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="505" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24200,7 +24218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="506" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24235,7 +24253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="507" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24270,7 +24288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="508" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24305,7 +24323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="509" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24340,7 +24358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="510" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24375,7 +24393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24410,7 +24428,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="512" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="2" t="s">
         <v>11</v>
       </c>
@@ -24445,7 +24463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="513" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="2" t="s">
         <v>11</v>
       </c>
@@ -24480,7 +24498,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="514" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="2" t="s">
         <v>11</v>
       </c>
@@ -24515,7 +24533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="515" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="2" t="s">
         <v>11</v>
       </c>
@@ -24550,7 +24568,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="516" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="2" t="s">
         <v>11</v>
       </c>
@@ -24585,7 +24603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="2" t="s">
         <v>11</v>
       </c>
@@ -24620,7 +24638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="518" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="2" t="s">
         <v>11</v>
       </c>
@@ -24655,7 +24673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="519" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="2" t="s">
         <v>11</v>
       </c>
@@ -24690,7 +24708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="520" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24725,7 +24743,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="521" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24760,7 +24778,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="522" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24795,7 +24813,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="523" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24830,7 +24848,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="524" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24865,7 +24883,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="525" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24900,7 +24918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="526" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24935,7 +24953,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="527" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
         <v>1011</v>
       </c>
@@ -24970,7 +24988,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="528" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25005,7 +25023,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="529" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
         <v>11</v>
       </c>
@@ -25040,7 +25058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="530" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
         <v>11</v>
       </c>
@@ -25075,7 +25093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="531" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
         <v>11</v>
       </c>
@@ -25110,7 +25128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="532" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
         <v>11</v>
       </c>
@@ -25145,7 +25163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="533" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
         <v>11</v>
       </c>
@@ -25180,7 +25198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="534" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25215,7 +25233,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="535" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25250,7 +25268,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="536" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25285,7 +25303,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="537" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25320,7 +25338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="538" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25355,7 +25373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="539" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25390,7 +25408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="540" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25425,7 +25443,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="541" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25460,7 +25478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="542" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="2" t="s">
         <v>11</v>
       </c>
@@ -25495,7 +25513,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="543" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="2" t="s">
         <v>1011</v>
       </c>
@@ -25530,7 +25548,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="544" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="2" t="s">
         <v>11</v>
       </c>
@@ -25565,7 +25583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="545" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="2" t="s">
         <v>11</v>
       </c>
@@ -25600,7 +25618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="546" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="2" t="s">
         <v>11</v>
       </c>
@@ -25635,7 +25653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="547" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="2" t="s">
         <v>11</v>
       </c>
@@ -25670,7 +25688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="548" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="2" t="s">
         <v>11</v>
       </c>
@@ -25705,7 +25723,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="549" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="2" t="s">
         <v>11</v>
       </c>
@@ -25740,7 +25758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="550" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="2" t="s">
         <v>11</v>
       </c>
@@ -25775,7 +25793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="551" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="2" t="s">
         <v>11</v>
       </c>
@@ -25810,7 +25828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="552" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="2" t="s">
         <v>11</v>
       </c>
@@ -25845,7 +25863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="553" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="2" t="s">
         <v>11</v>
       </c>
@@ -25880,7 +25898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="554" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="2" t="s">
         <v>11</v>
       </c>
@@ -25915,7 +25933,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="555" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="2" t="s">
         <v>11</v>
       </c>
@@ -25950,7 +25968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="556" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="2" t="s">
         <v>11</v>
       </c>
@@ -25985,7 +26003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="557" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="2" t="s">
         <v>11</v>
       </c>
@@ -26020,7 +26038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="558" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="2" t="s">
         <v>11</v>
       </c>
@@ -26055,7 +26073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="559" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="2" t="s">
         <v>11</v>
       </c>
@@ -26090,7 +26108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="560" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="2" t="s">
         <v>11</v>
       </c>
@@ -26125,7 +26143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="561" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="2" t="s">
         <v>11</v>
       </c>
@@ -26160,7 +26178,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="562" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="2" t="s">
         <v>11</v>
       </c>
@@ -26195,7 +26213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="563" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="2" t="s">
         <v>11</v>
       </c>
@@ -26230,7 +26248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="564" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="2" t="s">
         <v>11</v>
       </c>
@@ -26265,7 +26283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="565" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="2" t="s">
         <v>11</v>
       </c>
@@ -26300,7 +26318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="566" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="2" t="s">
         <v>11</v>
       </c>
@@ -26335,7 +26353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="567" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="2" t="s">
         <v>11</v>
       </c>
@@ -26370,7 +26388,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="568" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
         <v>11</v>
       </c>
@@ -26405,7 +26423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="569" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="2" t="s">
         <v>11</v>
       </c>
@@ -26440,7 +26458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="570" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="2" t="s">
         <v>11</v>
       </c>
@@ -26475,7 +26493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="571" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="2" t="s">
         <v>11</v>
       </c>
@@ -26510,7 +26528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="572" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="2" t="s">
         <v>11</v>
       </c>
@@ -26545,7 +26563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="573" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="2" t="s">
         <v>11</v>
       </c>
@@ -26580,7 +26598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="574" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="2" t="s">
         <v>11</v>
       </c>
@@ -26615,7 +26633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="575" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26650,7 +26668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="576" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26685,7 +26703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="577" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26720,7 +26738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="578" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26755,7 +26773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="579" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26790,7 +26808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="580" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26825,7 +26843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="581" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26860,7 +26878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="582" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26895,7 +26913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="583" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26930,7 +26948,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="584" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="2" t="s">
         <v>1306</v>
       </c>
@@ -26965,7 +26983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="585" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27000,7 +27018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="586" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27035,7 +27053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="587" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27070,7 +27088,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="588" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27105,7 +27123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27140,7 +27158,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="590" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27175,7 +27193,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="591" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27210,7 +27228,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="592" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27245,7 +27263,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="593" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27280,7 +27298,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="594" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27315,7 +27333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="595" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27350,7 +27368,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="596" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27364,7 +27382,7 @@
         <v>1337</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F596" s="2" t="s">
         <v>16</v>
@@ -27385,7 +27403,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="597" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27399,7 +27417,7 @@
         <v>1337</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F597" s="2" t="s">
         <v>16</v>
@@ -27420,7 +27438,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="598" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27455,7 +27473,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="599" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27490,7 +27508,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="600" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27525,7 +27543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="601" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27560,7 +27578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="602" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27595,7 +27613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="603" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27630,7 +27648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="604" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="2" t="s">
         <v>1335</v>
       </c>
@@ -27665,7 +27683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="605" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27700,7 +27718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="606" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27735,7 +27753,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="607" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27770,7 +27788,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="608" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27805,7 +27823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="609" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27840,7 +27858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="610" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27875,7 +27893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="611" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27910,7 +27928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="612" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27945,7 +27963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="613" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27980,7 +27998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="614" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28015,7 +28033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="615" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28050,7 +28068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="616" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28085,7 +28103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="617" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28120,7 +28138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="618" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28155,7 +28173,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="619" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28190,7 +28208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="620" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="2" t="s">
         <v>1306</v>
       </c>
@@ -28225,7 +28243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="621" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28260,7 +28278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="622" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28295,7 +28313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="623" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28330,7 +28348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="624" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28365,7 +28383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="625" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28400,7 +28418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="626" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28435,7 +28453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="627" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28470,7 +28488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="628" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="2" t="s">
         <v>1306</v>
       </c>
@@ -28505,7 +28523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="629" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28540,7 +28558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="630" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28575,7 +28593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="631" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28610,7 +28628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="632" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28645,7 +28663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="633" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28680,7 +28698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="634" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28715,7 +28733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="635" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28750,7 +28768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="636" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28785,7 +28803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="637" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28820,7 +28838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="638" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28855,7 +28873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="639" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28890,7 +28908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="640" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="2" t="s">
         <v>1306</v>
       </c>
@@ -28925,7 +28943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="641" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="2" t="s">
         <v>1306</v>
       </c>
@@ -28960,7 +28978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="642" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="2" t="s">
         <v>1306</v>
       </c>
@@ -28995,7 +29013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="643" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29030,7 +29048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="644" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29065,7 +29083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="645" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29100,7 +29118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="646" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29135,7 +29153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="647" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29170,7 +29188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="648" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29205,7 +29223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="649" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29240,7 +29258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="650" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29254,7 +29272,7 @@
         <v>1337</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F650" s="2" t="s">
         <v>16</v>
@@ -29275,7 +29293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="651" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29289,7 +29307,7 @@
         <v>1337</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F651" s="2" t="s">
         <v>16</v>
@@ -29310,7 +29328,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="652" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29345,7 +29363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="653" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29380,7 +29398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="654" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29415,7 +29433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="655" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29450,7 +29468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="656" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29485,7 +29503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="657" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29499,7 +29517,7 @@
         <v>1337</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F657" s="2" t="s">
         <v>16</v>
@@ -29520,7 +29538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="658" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29534,7 +29552,7 @@
         <v>1337</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F658" s="2" t="s">
         <v>16</v>
@@ -29555,7 +29573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="659" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29590,7 +29608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="660" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29625,7 +29643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="661" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29660,7 +29678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="662" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29695,7 +29713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="663" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="2" t="s">
         <v>1306</v>
       </c>
@@ -29730,7 +29748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="664" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29765,7 +29783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="665" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29800,7 +29818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="666" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29835,7 +29853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="667" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29870,7 +29888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="668" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29905,7 +29923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="669" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29940,7 +29958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="670" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="2" t="s">
         <v>1335</v>
       </c>
@@ -29975,7 +29993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="671" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30010,7 +30028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="672" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30045,7 +30063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="673" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30080,7 +30098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="674" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30115,7 +30133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="675" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30150,7 +30168,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="676" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30185,7 +30203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="677" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30220,7 +30238,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="678" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30255,7 +30273,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="679" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30290,7 +30308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="680" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30304,7 +30322,7 @@
         <v>1337</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F680" s="2" t="s">
         <v>16</v>
@@ -30325,7 +30343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="681" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30339,7 +30357,7 @@
         <v>1337</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F681" s="2" t="s">
         <v>16</v>
@@ -30360,7 +30378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="682" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30395,7 +30413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="683" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30430,7 +30448,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="684" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30465,7 +30483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="685" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="2" t="s">
         <v>1335</v>
       </c>
@@ -30500,7 +30518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="686" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30535,7 +30553,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="687" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30570,7 +30588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="688" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30605,7 +30623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="689" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30640,7 +30658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="690" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30675,7 +30693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="691" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30710,7 +30728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="692" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30745,7 +30763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="693" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30780,7 +30798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="694" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30815,7 +30833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="695" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30850,7 +30868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="696" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30885,7 +30903,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="697" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30920,7 +30938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="698" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30955,7 +30973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="699" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="2" t="s">
         <v>1306</v>
       </c>
@@ -30990,7 +31008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="700" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31025,7 +31043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="701" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31060,7 +31078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="702" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31095,7 +31113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="703" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31130,7 +31148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="704" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31165,7 +31183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="705" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31200,7 +31218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="706" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31235,7 +31253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="707" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31270,7 +31288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="708" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31305,7 +31323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="709" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31340,7 +31358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="710" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31375,7 +31393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="711" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31410,7 +31428,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="712" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31445,7 +31463,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="713" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31480,7 +31498,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="714" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31515,7 +31533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="715" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31550,7 +31568,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="716" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31585,7 +31603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="717" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31620,7 +31638,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="718" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31655,7 +31673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="719" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31690,7 +31708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="720" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31725,7 +31743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="721" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31760,7 +31778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="722" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31795,7 +31813,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="723" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31830,7 +31848,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="724" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31865,7 +31883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="725" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31900,7 +31918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="726" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31935,7 +31953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="727" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="2" t="s">
         <v>1306</v>
       </c>
@@ -31970,7 +31988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="728" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32005,7 +32023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="729" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32040,7 +32058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="730" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32075,7 +32093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="731" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32110,7 +32128,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="732" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32145,7 +32163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="733" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32180,7 +32198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="734" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32215,7 +32233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="735" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32250,7 +32268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="736" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32285,7 +32303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="737" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32320,7 +32338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="738" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32355,7 +32373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="739" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32390,7 +32408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="740" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32425,7 +32443,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="741" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32460,7 +32478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="742" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32495,7 +32513,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="743" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32530,7 +32548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="744" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32565,7 +32583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="745" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32600,7 +32618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="746" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32635,7 +32653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="747" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A747" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32670,7 +32688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="748" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32705,7 +32723,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="749" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32740,7 +32758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="750" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32775,7 +32793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="751" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32810,7 +32828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="752" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32845,7 +32863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="753" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32880,7 +32898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="754" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32915,7 +32933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="755" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32950,7 +32968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="756" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="2" t="s">
         <v>1306</v>
       </c>
@@ -32985,7 +33003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="757" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33020,7 +33038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="758" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33055,7 +33073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="759" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33090,7 +33108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="760" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33125,7 +33143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="761" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33160,7 +33178,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="762" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33195,7 +33213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="763" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33230,7 +33248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="764" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33265,7 +33283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="765" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33300,7 +33318,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="766" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33335,7 +33353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="767" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33370,7 +33388,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="768" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33405,7 +33423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="769" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33440,7 +33458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="770" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33475,7 +33493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="771" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33510,7 +33528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="772" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33545,7 +33563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="773" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33580,7 +33598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="774" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33615,7 +33633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="775" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33650,7 +33668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="776" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33685,7 +33703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="777" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33720,7 +33738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="778" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33755,7 +33773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="779" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33790,7 +33808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="780" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33825,7 +33843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="781" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33860,7 +33878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="782" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33895,7 +33913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="783" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33930,7 +33948,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="784" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="2" t="s">
         <v>1306</v>
       </c>
@@ -33965,7 +33983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="785" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="2" t="s">
         <v>1306</v>
       </c>
@@ -34000,7 +34018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="786" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="2" t="s">
         <v>1306</v>
       </c>
@@ -34035,7 +34053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="787" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="2" t="s">
         <v>1306</v>
       </c>
@@ -34070,7 +34088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="788" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="2" t="s">
         <v>11</v>
       </c>
@@ -34105,7 +34123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="789" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="2" t="s">
         <v>11</v>
       </c>
@@ -34140,7 +34158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="790" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="2" t="s">
         <v>11</v>
       </c>
@@ -34175,7 +34193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="791" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="2" t="s">
         <v>11</v>
       </c>
@@ -34210,7 +34228,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="792" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="2" t="s">
         <v>11</v>
       </c>
@@ -34245,7 +34263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="793" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="2" t="s">
         <v>11</v>
       </c>
@@ -34280,7 +34298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="794" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="2" t="s">
         <v>11</v>
       </c>
@@ -34315,7 +34333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="795" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="2" t="s">
         <v>11</v>
       </c>
@@ -34350,7 +34368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="796" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="2" t="s">
         <v>11</v>
       </c>
@@ -34385,7 +34403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="797" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="2" t="s">
         <v>11</v>
       </c>
@@ -34420,7 +34438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="798" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="2" t="s">
         <v>11</v>
       </c>
@@ -34455,7 +34473,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="799" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="2" t="s">
         <v>11</v>
       </c>
@@ -34490,7 +34508,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="800" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="2" t="s">
         <v>11</v>
       </c>
@@ -34525,7 +34543,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="801" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="2" t="s">
         <v>11</v>
       </c>
@@ -34560,7 +34578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="802" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="2" t="s">
         <v>11</v>
       </c>
@@ -34595,7 +34613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="803" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="2" t="s">
         <v>11</v>
       </c>
@@ -34630,7 +34648,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="804" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="2" t="s">
         <v>11</v>
       </c>
@@ -34665,7 +34683,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="805" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="2" t="s">
         <v>11</v>
       </c>
@@ -34700,7 +34718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="806" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="2" t="s">
         <v>11</v>
       </c>
@@ -34735,7 +34753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="807" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="2" t="s">
         <v>11</v>
       </c>
@@ -34770,7 +34788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="808" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="2" t="s">
         <v>11</v>
       </c>
@@ -34805,7 +34823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="809" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="2" t="s">
         <v>11</v>
       </c>
@@ -34840,7 +34858,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="810" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="2" t="s">
         <v>11</v>
       </c>
@@ -34875,7 +34893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="811" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="2" t="s">
         <v>11</v>
       </c>
@@ -34910,7 +34928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="812" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="2" t="s">
         <v>11</v>
       </c>
@@ -34945,7 +34963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="813" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="2" t="s">
         <v>11</v>
       </c>
@@ -34980,7 +34998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="814" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="2" t="s">
         <v>11</v>
       </c>
@@ -35015,7 +35033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="815" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="2" t="s">
         <v>11</v>
       </c>
@@ -35050,7 +35068,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="816" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="2" t="s">
         <v>11</v>
       </c>
@@ -35085,7 +35103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="817" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="2" t="s">
         <v>11</v>
       </c>
@@ -35120,7 +35138,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="818" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="2" t="s">
         <v>11</v>
       </c>
@@ -35155,7 +35173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="819" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="2" t="s">
         <v>11</v>
       </c>
@@ -35190,7 +35208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="820" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="2" t="s">
         <v>11</v>
       </c>
@@ -35225,7 +35243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="821" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="2" t="s">
         <v>11</v>
       </c>
@@ -35260,7 +35278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="822" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="2" t="s">
         <v>11</v>
       </c>
@@ -35295,7 +35313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="823" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="2" t="s">
         <v>11</v>
       </c>
@@ -35330,7 +35348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="824" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="2" t="s">
         <v>11</v>
       </c>
@@ -35365,7 +35383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="825" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="2" t="s">
         <v>11</v>
       </c>
@@ -35400,7 +35418,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="826" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="2" t="s">
         <v>11</v>
       </c>
@@ -35435,7 +35453,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="827" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="2" t="s">
         <v>11</v>
       </c>
@@ -35470,7 +35488,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="828" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="2" t="s">
         <v>11</v>
       </c>
@@ -35505,7 +35523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="829" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="2" t="s">
         <v>11</v>
       </c>
@@ -35540,7 +35558,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="830" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="2" t="s">
         <v>11</v>
       </c>
@@ -35575,7 +35593,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="831" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="2" t="s">
         <v>11</v>
       </c>
@@ -35610,7 +35628,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="832" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35645,7 +35663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="833" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35680,7 +35698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="834" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35715,7 +35733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="835" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35750,7 +35768,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="836" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35785,7 +35803,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="837" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35820,7 +35838,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="838" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35855,7 +35873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="839" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35890,7 +35908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="840" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A840" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35925,7 +35943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="841" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35960,7 +35978,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="842" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="2" t="s">
         <v>1908</v>
       </c>
@@ -35995,7 +36013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="843" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36030,7 +36048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="844" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36065,7 +36083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="845" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36100,7 +36118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="846" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36135,7 +36153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="847" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36170,7 +36188,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="848" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36205,7 +36223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="849" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36240,7 +36258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="850" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36275,7 +36293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="851" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36310,7 +36328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="852" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36345,7 +36363,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="853" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36380,7 +36398,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="854" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36415,7 +36433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="855" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36450,7 +36468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="856" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36485,7 +36503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="857" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36520,7 +36538,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="858" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36555,7 +36573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="859" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36590,7 +36608,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="860" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36625,7 +36643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="861" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36660,7 +36678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="862" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36695,7 +36713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="863" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36730,7 +36748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="864" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36765,7 +36783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="865" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36800,7 +36818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="866" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36835,7 +36853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="867" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36870,7 +36888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="868" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36905,7 +36923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="869" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36940,7 +36958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="870" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="2" t="s">
         <v>1908</v>
       </c>
@@ -36975,7 +36993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="871" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37010,7 +37028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="872" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37045,7 +37063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="873" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37080,7 +37098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="874" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37115,7 +37133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="875" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37150,7 +37168,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="876" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37185,7 +37203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="877" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37220,7 +37238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="878" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37255,7 +37273,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="879" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37290,7 +37308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="880" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37325,7 +37343,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="881" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37360,7 +37378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="882" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37395,7 +37413,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="883" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37430,7 +37448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="884" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37465,7 +37483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="885" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37500,7 +37518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="886" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37535,7 +37553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="887" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37570,7 +37588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="888" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37605,7 +37623,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="889" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37640,7 +37658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="890" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37675,7 +37693,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="891" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37710,7 +37728,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="892" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37745,7 +37763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="893" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37780,7 +37798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="894" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37815,7 +37833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="895" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37850,7 +37868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="896" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37885,7 +37903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="897" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37920,7 +37938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="898" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37955,7 +37973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="899" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="2" t="s">
         <v>1908</v>
       </c>
@@ -37990,7 +38008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="900" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38025,7 +38043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="901" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38060,7 +38078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="902" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38095,7 +38113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="903" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38130,7 +38148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="904" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38165,7 +38183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="905" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38200,7 +38218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="906" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38235,7 +38253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="907" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="2" t="s">
         <v>1908</v>
       </c>
@@ -38270,7 +38288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="908" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="2" t="s">
         <v>1908</v>
       </c>
